--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:18</t>
+    <t xml:space="preserve">2026-09-09 23:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:13</t>
+    <t xml:space="preserve">2026-09-17 14:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:09</t>
+    <t xml:space="preserve">2026-09-23 12:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:38</t>
+    <t xml:space="preserve">2026-10-02 14:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2024_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:49</t>
+    <t xml:space="preserve">2026-10-05 11:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1062,7 +1062,7 @@
         <v>2024</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>448819.62</v>
+        <v>448819.63</v>
       </c>
     </row>
     <row r="28">
@@ -1079,7 +1079,7 @@
         <v>2024</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>436469.12</v>
+        <v>436469.13</v>
       </c>
     </row>
     <row r="29">
@@ -1181,7 +1181,7 @@
         <v>2024</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>403550.62</v>
+        <v>403550.63</v>
       </c>
     </row>
     <row r="35">
@@ -1368,7 +1368,7 @@
         <v>2024</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>328509.62</v>
+        <v>328509.63</v>
       </c>
     </row>
     <row r="46">
